--- a/TDXapp/tdxAppData/tdxApiZzGzIndexs.xlsx
+++ b/TDXapp/tdxAppData/tdxApiZzGzIndexs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3466" uniqueCount="1390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3596" uniqueCount="1435">
   <si>
     <t>IndexCode</t>
   </si>
@@ -1427,6 +1427,12 @@
     <t>港股通医药C</t>
   </si>
   <si>
+    <t>930967</t>
+  </si>
+  <si>
+    <t>港股通信息C</t>
+  </si>
+  <si>
     <t>930975</t>
   </si>
   <si>
@@ -1829,6 +1835,12 @@
     <t>港股通汽车</t>
   </si>
   <si>
+    <t>931241</t>
+  </si>
+  <si>
+    <t>家居家电</t>
+  </si>
+  <si>
     <t>931243</t>
   </si>
   <si>
@@ -2459,6 +2471,12 @@
     <t>农牧主题</t>
   </si>
   <si>
+    <t>931785</t>
+  </si>
+  <si>
+    <t>智选沪深港科技50</t>
+  </si>
+  <si>
     <t>931787</t>
   </si>
   <si>
@@ -2603,6 +2621,12 @@
     <t>绿色电力</t>
   </si>
   <si>
+    <t>931946</t>
+  </si>
+  <si>
+    <t>畜牧养殖</t>
+  </si>
+  <si>
     <t>931992</t>
   </si>
   <si>
@@ -2795,6 +2819,12 @@
     <t>集成电路</t>
   </si>
   <si>
+    <t>932088</t>
+  </si>
+  <si>
+    <t>全指航空</t>
+  </si>
+  <si>
     <t>932094</t>
   </si>
   <si>
@@ -2942,12 +2972,111 @@
     <t>A500红利低波</t>
   </si>
   <si>
+    <t>932431</t>
+  </si>
+  <si>
+    <t>300质量</t>
+  </si>
+  <si>
+    <t>932444</t>
+  </si>
+  <si>
+    <t>互联互通中国50HK</t>
+  </si>
+  <si>
+    <t>932447</t>
+  </si>
+  <si>
+    <t>中新亚洲100红利</t>
+  </si>
+  <si>
+    <t>932456</t>
+  </si>
+  <si>
+    <t>科创创业AI</t>
+  </si>
+  <si>
+    <t>932462</t>
+  </si>
+  <si>
+    <t>互联互通中国50US</t>
+  </si>
+  <si>
+    <t>932501</t>
+  </si>
+  <si>
+    <t>互联互通中国50人</t>
+  </si>
+  <si>
     <t>932536</t>
   </si>
   <si>
     <t>航运发展</t>
   </si>
   <si>
+    <t>932537</t>
+  </si>
+  <si>
+    <t>互联互通中国50SG</t>
+  </si>
+  <si>
+    <t>932578</t>
+  </si>
+  <si>
+    <t>932583</t>
+  </si>
+  <si>
+    <t>932585</t>
+  </si>
+  <si>
+    <t>互联互通中国50红</t>
+  </si>
+  <si>
+    <t>932589</t>
+  </si>
+  <si>
+    <t>932590</t>
+  </si>
+  <si>
+    <t>932592</t>
+  </si>
+  <si>
+    <t>互联互通中国50</t>
+  </si>
+  <si>
+    <t>932593</t>
+  </si>
+  <si>
+    <t>932597</t>
+  </si>
+  <si>
+    <t>中新亚洲100USD</t>
+  </si>
+  <si>
+    <t>932598</t>
+  </si>
+  <si>
+    <t>932600</t>
+  </si>
+  <si>
+    <t>中新亚洲100SGD</t>
+  </si>
+  <si>
+    <t>932601</t>
+  </si>
+  <si>
+    <t>932603</t>
+  </si>
+  <si>
+    <t>中新亚洲100HKD</t>
+  </si>
+  <si>
+    <t>932607</t>
+  </si>
+  <si>
+    <t>中新亚洲100</t>
+  </si>
+  <si>
     <t>933000</t>
   </si>
   <si>
@@ -3515,7 +3644,7 @@
     <t>H30106</t>
   </si>
   <si>
-    <t>H300金融服务</t>
+    <t>港股通金融服务</t>
   </si>
   <si>
     <t>H30124</t>
@@ -3546,6 +3675,12 @@
   </si>
   <si>
     <t>半导体</t>
+  </si>
+  <si>
+    <t>H30192</t>
+  </si>
+  <si>
+    <t>食品</t>
   </si>
   <si>
     <t>H30198</t>
@@ -5190,8 +5325,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F693"/>
+  <dimension ref="A1:F719"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="17.75" customWidth="1"/>
+    <col min="3" max="3" width="8.125" customWidth="1"/>
+    <col min="4" max="5" width="12.875" customWidth="1"/>
+    <col min="6" max="6" width="7.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
@@ -14498,7 +14640,7 @@
         <v>936</v>
       </c>
       <c r="B466" t="s">
-        <v>583</v>
+        <v>937</v>
       </c>
       <c r="C466" t="s">
         <v>8</v>
@@ -14515,10 +14657,10 @@
     </row>
     <row r="467" spans="1:6">
       <c r="A467" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B467" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C467" t="s">
         <v>8</v>
@@ -14535,10 +14677,10 @@
     </row>
     <row r="468" spans="1:6">
       <c r="A468" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B468" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C468" t="s">
         <v>8</v>
@@ -14555,10 +14697,10 @@
     </row>
     <row r="469" spans="1:6">
       <c r="A469" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B469" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C469" t="s">
         <v>8</v>
@@ -14575,10 +14717,10 @@
     </row>
     <row r="470" spans="1:6">
       <c r="A470" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B470" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C470" t="s">
         <v>8</v>
@@ -14595,10 +14737,10 @@
     </row>
     <row r="471" spans="1:6">
       <c r="A471" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B471" t="s">
-        <v>946</v>
+        <v>585</v>
       </c>
       <c r="C471" t="s">
         <v>8</v>
@@ -15118,7 +15260,7 @@
         <v>997</v>
       </c>
       <c r="B497" t="s">
-        <v>998</v>
+        <v>986</v>
       </c>
       <c r="C497" t="s">
         <v>8</v>
@@ -15135,10 +15277,10 @@
     </row>
     <row r="498" spans="1:6">
       <c r="A498" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B498" t="s">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="C498" t="s">
         <v>8</v>
@@ -15155,10 +15297,10 @@
     </row>
     <row r="499" spans="1:6">
       <c r="A499" s="1" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B499" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C499" t="s">
         <v>8</v>
@@ -15175,10 +15317,10 @@
     </row>
     <row r="500" spans="1:6">
       <c r="A500" s="1" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B500" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C500" t="s">
         <v>8</v>
@@ -15195,10 +15337,10 @@
     </row>
     <row r="501" spans="1:6">
       <c r="A501" s="1" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B501" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="C501" t="s">
         <v>8</v>
@@ -15215,10 +15357,10 @@
     </row>
     <row r="502" spans="1:6">
       <c r="A502" s="1" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B502" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="C502" t="s">
         <v>8</v>
@@ -15235,10 +15377,10 @@
     </row>
     <row r="503" spans="1:6">
       <c r="A503" s="1" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="B503" t="s">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="C503" t="s">
         <v>8</v>
@@ -15255,10 +15397,10 @@
     </row>
     <row r="504" spans="1:6">
       <c r="A504" s="1" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="B504" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="C504" t="s">
         <v>8</v>
@@ -15275,10 +15417,10 @@
     </row>
     <row r="505" spans="1:6">
       <c r="A505" s="1" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="B505" t="s">
-        <v>1014</v>
+        <v>1000</v>
       </c>
       <c r="C505" t="s">
         <v>8</v>
@@ -15295,10 +15437,10 @@
     </row>
     <row r="506" spans="1:6">
       <c r="A506" s="1" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="B506" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="C506" t="s">
         <v>8</v>
@@ -15315,10 +15457,10 @@
     </row>
     <row r="507" spans="1:6">
       <c r="A507" s="1" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="B507" t="s">
-        <v>1018</v>
+        <v>986</v>
       </c>
       <c r="C507" t="s">
         <v>8</v>
@@ -15335,10 +15477,10 @@
     </row>
     <row r="508" spans="1:6">
       <c r="A508" s="1" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="B508" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="C508" t="s">
         <v>8</v>
@@ -15355,10 +15497,10 @@
     </row>
     <row r="509" spans="1:6">
       <c r="A509" s="1" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
       <c r="B509" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
       <c r="C509" t="s">
         <v>8</v>
@@ -15375,10 +15517,10 @@
     </row>
     <row r="510" spans="1:6">
       <c r="A510" s="1" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="B510" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="C510" t="s">
         <v>8</v>
@@ -15395,10 +15537,10 @@
     </row>
     <row r="511" spans="1:6">
       <c r="A511" s="1" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="B511" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="C511" t="s">
         <v>8</v>
@@ -15415,10 +15557,10 @@
     </row>
     <row r="512" spans="1:6">
       <c r="A512" s="1" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="B512" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="C512" t="s">
         <v>8</v>
@@ -15435,10 +15577,10 @@
     </row>
     <row r="513" spans="1:6">
       <c r="A513" s="1" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="B513" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="C513" t="s">
         <v>8</v>
@@ -15455,10 +15597,10 @@
     </row>
     <row r="514" spans="1:6">
       <c r="A514" s="1" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="B514" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="C514" t="s">
         <v>8</v>
@@ -15475,10 +15617,10 @@
     </row>
     <row r="515" spans="1:6">
       <c r="A515" s="1" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="B515" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="C515" t="s">
         <v>8</v>
@@ -15495,10 +15637,10 @@
     </row>
     <row r="516" spans="1:6">
       <c r="A516" s="1" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="B516" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="C516" t="s">
         <v>8</v>
@@ -15515,10 +15657,10 @@
     </row>
     <row r="517" spans="1:6">
       <c r="A517" s="1" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="B517" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="C517" t="s">
         <v>8</v>
@@ -15535,10 +15677,10 @@
     </row>
     <row r="518" spans="1:6">
       <c r="A518" s="1" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="B518" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="C518" t="s">
         <v>8</v>
@@ -15555,10 +15697,10 @@
     </row>
     <row r="519" spans="1:6">
       <c r="A519" s="1" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="B519" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="C519" t="s">
         <v>8</v>
@@ -15575,10 +15717,10 @@
     </row>
     <row r="520" spans="1:6">
       <c r="A520" s="1" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="B520" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="C520" t="s">
         <v>8</v>
@@ -15595,10 +15737,10 @@
     </row>
     <row r="521" spans="1:6">
       <c r="A521" s="1" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="B521" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="C521" t="s">
         <v>8</v>
@@ -15615,10 +15757,10 @@
     </row>
     <row r="522" spans="1:6">
       <c r="A522" s="1" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="B522" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="C522" t="s">
         <v>8</v>
@@ -15635,10 +15777,10 @@
     </row>
     <row r="523" spans="1:6">
       <c r="A523" s="1" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="B523" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="C523" t="s">
         <v>8</v>
@@ -15655,10 +15797,10 @@
     </row>
     <row r="524" spans="1:6">
       <c r="A524" s="1" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="B524" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="C524" t="s">
         <v>8</v>
@@ -15675,10 +15817,10 @@
     </row>
     <row r="525" spans="1:6">
       <c r="A525" s="1" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="B525" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="C525" t="s">
         <v>8</v>
@@ -15695,10 +15837,10 @@
     </row>
     <row r="526" spans="1:6">
       <c r="A526" s="1" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="B526" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="C526" t="s">
         <v>8</v>
@@ -15715,10 +15857,10 @@
     </row>
     <row r="527" spans="1:6">
       <c r="A527" s="1" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="B527" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="C527" t="s">
         <v>8</v>
@@ -15735,10 +15877,10 @@
     </row>
     <row r="528" spans="1:6">
       <c r="A528" s="1" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="B528" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="C528" t="s">
         <v>8</v>
@@ -15755,10 +15897,10 @@
     </row>
     <row r="529" spans="1:6">
       <c r="A529" s="1" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="B529" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="C529" t="s">
         <v>8</v>
@@ -15775,10 +15917,10 @@
     </row>
     <row r="530" spans="1:6">
       <c r="A530" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="B530" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="C530" t="s">
         <v>8</v>
@@ -15795,10 +15937,10 @@
     </row>
     <row r="531" spans="1:6">
       <c r="A531" s="1" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="B531" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="C531" t="s">
         <v>8</v>
@@ -15815,10 +15957,10 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" s="1" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="B532" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="C532" t="s">
         <v>8</v>
@@ -15835,10 +15977,10 @@
     </row>
     <row r="533" spans="1:6">
       <c r="A533" s="1" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="B533" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="C533" t="s">
         <v>8</v>
@@ -15855,10 +15997,10 @@
     </row>
     <row r="534" spans="1:6">
       <c r="A534" s="1" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="B534" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="C534" t="s">
         <v>8</v>
@@ -15875,10 +16017,10 @@
     </row>
     <row r="535" spans="1:6">
       <c r="A535" s="1" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="B535" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="C535" t="s">
         <v>8</v>
@@ -15895,10 +16037,10 @@
     </row>
     <row r="536" spans="1:6">
       <c r="A536" s="1" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="B536" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
       <c r="C536" t="s">
         <v>8</v>
@@ -15915,10 +16057,10 @@
     </row>
     <row r="537" spans="1:6">
       <c r="A537" s="1" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
       <c r="B537" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
       <c r="C537" t="s">
         <v>8</v>
@@ -15935,10 +16077,10 @@
     </row>
     <row r="538" spans="1:6">
       <c r="A538" s="1" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="B538" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="C538" t="s">
         <v>8</v>
@@ -15955,10 +16097,10 @@
     </row>
     <row r="539" spans="1:6">
       <c r="A539" s="1" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
       <c r="B539" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
       <c r="C539" t="s">
         <v>8</v>
@@ -15975,10 +16117,10 @@
     </row>
     <row r="540" spans="1:6">
       <c r="A540" s="1" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="B540" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="C540" t="s">
         <v>8</v>
@@ -15995,10 +16137,10 @@
     </row>
     <row r="541" spans="1:6">
       <c r="A541" s="1" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="B541" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="C541" t="s">
         <v>8</v>
@@ -16015,10 +16157,10 @@
     </row>
     <row r="542" spans="1:6">
       <c r="A542" s="1" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="B542" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="C542" t="s">
         <v>8</v>
@@ -16035,10 +16177,10 @@
     </row>
     <row r="543" spans="1:6">
       <c r="A543" s="1" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B543" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C543" t="s">
         <v>8</v>
@@ -16055,10 +16197,10 @@
     </row>
     <row r="544" spans="1:6">
       <c r="A544" s="1" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="B544" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="C544" t="s">
         <v>8</v>
@@ -16075,10 +16217,10 @@
     </row>
     <row r="545" spans="1:6">
       <c r="A545" s="1" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="B545" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="C545" t="s">
         <v>8</v>
@@ -16095,10 +16237,10 @@
     </row>
     <row r="546" spans="1:6">
       <c r="A546" s="1" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="B546" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
       <c r="C546" t="s">
         <v>8</v>
@@ -16115,10 +16257,10 @@
     </row>
     <row r="547" spans="1:6">
       <c r="A547" s="1" t="s">
-        <v>1097</v>
+        <v>1090</v>
       </c>
       <c r="B547" t="s">
-        <v>1098</v>
+        <v>1091</v>
       </c>
       <c r="C547" t="s">
         <v>8</v>
@@ -16135,10 +16277,10 @@
     </row>
     <row r="548" spans="1:6">
       <c r="A548" s="1" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
       <c r="B548" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
       <c r="C548" t="s">
         <v>8</v>
@@ -16155,10 +16297,10 @@
     </row>
     <row r="549" spans="1:6">
       <c r="A549" s="1" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
       <c r="B549" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="C549" t="s">
         <v>8</v>
@@ -16175,10 +16317,10 @@
     </row>
     <row r="550" spans="1:6">
       <c r="A550" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="B550" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="C550" t="s">
         <v>8</v>
@@ -16195,10 +16337,10 @@
     </row>
     <row r="551" spans="1:6">
       <c r="A551" s="1" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="B551" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="C551" t="s">
         <v>8</v>
@@ -16215,10 +16357,10 @@
     </row>
     <row r="552" spans="1:6">
       <c r="A552" s="1" t="s">
-        <v>1107</v>
+        <v>1100</v>
       </c>
       <c r="B552" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="C552" t="s">
         <v>8</v>
@@ -16235,10 +16377,10 @@
     </row>
     <row r="553" spans="1:6">
       <c r="A553" s="1" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="B553" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
       <c r="C553" t="s">
         <v>8</v>
@@ -16255,10 +16397,10 @@
     </row>
     <row r="554" spans="1:6">
       <c r="A554" s="1" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="B554" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
       <c r="C554" t="s">
         <v>8</v>
@@ -16275,10 +16417,10 @@
     </row>
     <row r="555" spans="1:6">
       <c r="A555" s="1" t="s">
-        <v>1113</v>
+        <v>1106</v>
       </c>
       <c r="B555" t="s">
-        <v>1114</v>
+        <v>1107</v>
       </c>
       <c r="C555" t="s">
         <v>8</v>
@@ -16295,10 +16437,10 @@
     </row>
     <row r="556" spans="1:6">
       <c r="A556" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="B556" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="C556" t="s">
         <v>8</v>
@@ -16315,10 +16457,10 @@
     </row>
     <row r="557" spans="1:6">
       <c r="A557" s="1" t="s">
-        <v>1117</v>
+        <v>1110</v>
       </c>
       <c r="B557" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
       <c r="C557" t="s">
         <v>8</v>
@@ -16335,10 +16477,10 @@
     </row>
     <row r="558" spans="1:6">
       <c r="A558" s="1" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="B558" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
       <c r="C558" t="s">
         <v>8</v>
@@ -16355,10 +16497,10 @@
     </row>
     <row r="559" spans="1:6">
       <c r="A559" s="1" t="s">
-        <v>1121</v>
+        <v>1114</v>
       </c>
       <c r="B559" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="C559" t="s">
         <v>8</v>
@@ -16375,10 +16517,10 @@
     </row>
     <row r="560" spans="1:6">
       <c r="A560" s="1" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="B560" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
       <c r="C560" t="s">
         <v>8</v>
@@ -16395,10 +16537,10 @@
     </row>
     <row r="561" spans="1:6">
       <c r="A561" s="1" t="s">
-        <v>1125</v>
+        <v>1118</v>
       </c>
       <c r="B561" t="s">
-        <v>1126</v>
+        <v>1119</v>
       </c>
       <c r="C561" t="s">
         <v>8</v>
@@ -16415,10 +16557,10 @@
     </row>
     <row r="562" spans="1:6">
       <c r="A562" s="1" t="s">
-        <v>1127</v>
+        <v>1120</v>
       </c>
       <c r="B562" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="C562" t="s">
         <v>8</v>
@@ -16435,10 +16577,10 @@
     </row>
     <row r="563" spans="1:6">
       <c r="A563" s="1" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="B563" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
       <c r="C563" t="s">
         <v>8</v>
@@ -16455,10 +16597,10 @@
     </row>
     <row r="564" spans="1:6">
       <c r="A564" s="1" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
       <c r="B564" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="C564" t="s">
         <v>8</v>
@@ -16475,10 +16617,10 @@
     </row>
     <row r="565" spans="1:6">
       <c r="A565" s="1" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="B565" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
       <c r="C565" t="s">
         <v>8</v>
@@ -16495,10 +16637,10 @@
     </row>
     <row r="566" spans="1:6">
       <c r="A566" s="1" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
       <c r="B566" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="C566" t="s">
         <v>8</v>
@@ -16515,10 +16657,10 @@
     </row>
     <row r="567" spans="1:6">
       <c r="A567" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="B567" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="C567" t="s">
         <v>8</v>
@@ -16535,10 +16677,10 @@
     </row>
     <row r="568" spans="1:6">
       <c r="A568" s="1" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="B568" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="C568" t="s">
         <v>8</v>
@@ -16555,10 +16697,10 @@
     </row>
     <row r="569" spans="1:6">
       <c r="A569" s="1" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="B569" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="C569" t="s">
         <v>8</v>
@@ -16575,10 +16717,10 @@
     </row>
     <row r="570" spans="1:6">
       <c r="A570" s="1" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="B570" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="C570" t="s">
         <v>8</v>
@@ -16595,10 +16737,10 @@
     </row>
     <row r="571" spans="1:6">
       <c r="A571" s="1" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="B571" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="C571" t="s">
         <v>8</v>
@@ -16615,10 +16757,10 @@
     </row>
     <row r="572" spans="1:6">
       <c r="A572" s="1" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="B572" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="C572" t="s">
         <v>8</v>
@@ -16635,10 +16777,10 @@
     </row>
     <row r="573" spans="1:6">
       <c r="A573" s="1" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
       <c r="B573" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
       <c r="C573" t="s">
         <v>8</v>
@@ -16655,10 +16797,10 @@
     </row>
     <row r="574" spans="1:6">
       <c r="A574" s="1" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="B574" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
       <c r="C574" t="s">
         <v>8</v>
@@ -16675,10 +16817,10 @@
     </row>
     <row r="575" spans="1:6">
       <c r="A575" s="1" t="s">
-        <v>1153</v>
+        <v>1146</v>
       </c>
       <c r="B575" t="s">
-        <v>1154</v>
+        <v>1147</v>
       </c>
       <c r="C575" t="s">
         <v>8</v>
@@ -16695,10 +16837,10 @@
     </row>
     <row r="576" spans="1:6">
       <c r="A576" s="1" t="s">
-        <v>1155</v>
+        <v>1148</v>
       </c>
       <c r="B576" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
       <c r="C576" t="s">
         <v>8</v>
@@ -16715,10 +16857,10 @@
     </row>
     <row r="577" spans="1:6">
       <c r="A577" s="1" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
       <c r="B577" t="s">
-        <v>1158</v>
+        <v>1151</v>
       </c>
       <c r="C577" t="s">
         <v>8</v>
@@ -16735,10 +16877,10 @@
     </row>
     <row r="578" spans="1:6">
       <c r="A578" s="1" t="s">
-        <v>1159</v>
+        <v>1152</v>
       </c>
       <c r="B578" t="s">
-        <v>1160</v>
+        <v>1153</v>
       </c>
       <c r="C578" t="s">
         <v>8</v>
@@ -16755,10 +16897,10 @@
     </row>
     <row r="579" spans="1:6">
       <c r="A579" s="1" t="s">
-        <v>1161</v>
+        <v>1154</v>
       </c>
       <c r="B579" t="s">
-        <v>1162</v>
+        <v>1155</v>
       </c>
       <c r="C579" t="s">
         <v>8</v>
@@ -16775,10 +16917,10 @@
     </row>
     <row r="580" spans="1:6">
       <c r="A580" s="1" t="s">
-        <v>1163</v>
+        <v>1156</v>
       </c>
       <c r="B580" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="C580" t="s">
         <v>8</v>
@@ -16795,10 +16937,10 @@
     </row>
     <row r="581" spans="1:6">
       <c r="A581" s="1" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="B581" t="s">
-        <v>1166</v>
+        <v>1159</v>
       </c>
       <c r="C581" t="s">
         <v>8</v>
@@ -16815,10 +16957,10 @@
     </row>
     <row r="582" spans="1:6">
       <c r="A582" s="1" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
       <c r="B582" t="s">
-        <v>1168</v>
+        <v>1161</v>
       </c>
       <c r="C582" t="s">
         <v>8</v>
@@ -16835,10 +16977,10 @@
     </row>
     <row r="583" spans="1:6">
       <c r="A583" s="1" t="s">
-        <v>1169</v>
+        <v>1162</v>
       </c>
       <c r="B583" t="s">
-        <v>1170</v>
+        <v>1163</v>
       </c>
       <c r="C583" t="s">
         <v>8</v>
@@ -16855,10 +16997,10 @@
     </row>
     <row r="584" spans="1:6">
       <c r="A584" s="1" t="s">
-        <v>1171</v>
+        <v>1164</v>
       </c>
       <c r="B584" t="s">
-        <v>1172</v>
+        <v>1165</v>
       </c>
       <c r="C584" t="s">
         <v>8</v>
@@ -16875,10 +17017,10 @@
     </row>
     <row r="585" spans="1:6">
       <c r="A585" s="1" t="s">
-        <v>1173</v>
+        <v>1166</v>
       </c>
       <c r="B585" t="s">
-        <v>1174</v>
+        <v>1167</v>
       </c>
       <c r="C585" t="s">
         <v>8</v>
@@ -16895,10 +17037,10 @@
     </row>
     <row r="586" spans="1:6">
       <c r="A586" s="1" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
       <c r="B586" t="s">
-        <v>1176</v>
+        <v>1169</v>
       </c>
       <c r="C586" t="s">
         <v>8</v>
@@ -16915,10 +17057,10 @@
     </row>
     <row r="587" spans="1:6">
       <c r="A587" s="1" t="s">
-        <v>1177</v>
+        <v>1170</v>
       </c>
       <c r="B587" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
       <c r="C587" t="s">
         <v>8</v>
@@ -16935,10 +17077,10 @@
     </row>
     <row r="588" spans="1:6">
       <c r="A588" s="1" t="s">
-        <v>1179</v>
+        <v>1172</v>
       </c>
       <c r="B588" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="C588" t="s">
         <v>8</v>
@@ -16955,10 +17097,10 @@
     </row>
     <row r="589" spans="1:6">
       <c r="A589" s="1" t="s">
-        <v>1181</v>
+        <v>1174</v>
       </c>
       <c r="B589" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="C589" t="s">
         <v>8</v>
@@ -16975,10 +17117,10 @@
     </row>
     <row r="590" spans="1:6">
       <c r="A590" s="1" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="B590" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="C590" t="s">
         <v>8</v>
@@ -16995,10 +17137,10 @@
     </row>
     <row r="591" spans="1:6">
       <c r="A591" s="1" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="B591" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
       <c r="C591" t="s">
         <v>8</v>
@@ -17015,10 +17157,10 @@
     </row>
     <row r="592" spans="1:6">
       <c r="A592" s="1" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="B592" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
       <c r="C592" t="s">
         <v>8</v>
@@ -17035,10 +17177,10 @@
     </row>
     <row r="593" spans="1:6">
       <c r="A593" s="1" t="s">
-        <v>1189</v>
+        <v>1182</v>
       </c>
       <c r="B593" t="s">
-        <v>1190</v>
+        <v>1183</v>
       </c>
       <c r="C593" t="s">
         <v>8</v>
@@ -17055,10 +17197,10 @@
     </row>
     <row r="594" spans="1:6">
       <c r="A594" s="1" t="s">
-        <v>1191</v>
+        <v>1184</v>
       </c>
       <c r="B594" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="C594" t="s">
         <v>8</v>
@@ -17075,10 +17217,10 @@
     </row>
     <row r="595" spans="1:6">
       <c r="A595" s="1" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="B595" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
       <c r="C595" t="s">
         <v>8</v>
@@ -17095,10 +17237,10 @@
     </row>
     <row r="596" spans="1:6">
       <c r="A596" s="1" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="B596" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="C596" t="s">
         <v>8</v>
@@ -17115,10 +17257,10 @@
     </row>
     <row r="597" spans="1:6">
       <c r="A597" s="1" t="s">
-        <v>1197</v>
+        <v>1190</v>
       </c>
       <c r="B597" t="s">
-        <v>1198</v>
+        <v>1191</v>
       </c>
       <c r="C597" t="s">
         <v>8</v>
@@ -17135,10 +17277,10 @@
     </row>
     <row r="598" spans="1:6">
       <c r="A598" s="1" t="s">
-        <v>1199</v>
+        <v>1192</v>
       </c>
       <c r="B598" t="s">
-        <v>1200</v>
+        <v>1193</v>
       </c>
       <c r="C598" t="s">
         <v>8</v>
@@ -17155,10 +17297,10 @@
     </row>
     <row r="599" spans="1:6">
       <c r="A599" s="1" t="s">
-        <v>1201</v>
+        <v>1194</v>
       </c>
       <c r="B599" t="s">
-        <v>1202</v>
+        <v>1195</v>
       </c>
       <c r="C599" t="s">
         <v>8</v>
@@ -17175,10 +17317,10 @@
     </row>
     <row r="600" spans="1:6">
       <c r="A600" s="1" t="s">
-        <v>1203</v>
+        <v>1196</v>
       </c>
       <c r="B600" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="C600" t="s">
         <v>8</v>
@@ -17195,10 +17337,10 @@
     </row>
     <row r="601" spans="1:6">
       <c r="A601" s="1" t="s">
-        <v>1205</v>
+        <v>1198</v>
       </c>
       <c r="B601" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
       <c r="C601" t="s">
         <v>8</v>
@@ -17215,10 +17357,10 @@
     </row>
     <row r="602" spans="1:6">
       <c r="A602" s="1" t="s">
-        <v>1207</v>
+        <v>1200</v>
       </c>
       <c r="B602" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
       <c r="C602" t="s">
         <v>8</v>
@@ -17235,10 +17377,10 @@
     </row>
     <row r="603" spans="1:6">
       <c r="A603" s="1" t="s">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="B603" t="s">
-        <v>1210</v>
+        <v>1203</v>
       </c>
       <c r="C603" t="s">
         <v>8</v>
@@ -17255,10 +17397,10 @@
     </row>
     <row r="604" spans="1:6">
       <c r="A604" s="1" t="s">
-        <v>1211</v>
+        <v>1204</v>
       </c>
       <c r="B604" t="s">
-        <v>1212</v>
+        <v>1205</v>
       </c>
       <c r="C604" t="s">
         <v>8</v>
@@ -17275,10 +17417,10 @@
     </row>
     <row r="605" spans="1:6">
       <c r="A605" s="1" t="s">
-        <v>1213</v>
+        <v>1206</v>
       </c>
       <c r="B605" t="s">
-        <v>1214</v>
+        <v>1207</v>
       </c>
       <c r="C605" t="s">
         <v>8</v>
@@ -17295,10 +17437,10 @@
     </row>
     <row r="606" spans="1:6">
       <c r="A606" s="1" t="s">
-        <v>1215</v>
+        <v>1208</v>
       </c>
       <c r="B606" t="s">
-        <v>1216</v>
+        <v>1209</v>
       </c>
       <c r="C606" t="s">
         <v>8</v>
@@ -17315,10 +17457,10 @@
     </row>
     <row r="607" spans="1:6">
       <c r="A607" s="1" t="s">
-        <v>1217</v>
+        <v>1210</v>
       </c>
       <c r="B607" t="s">
-        <v>1218</v>
+        <v>1211</v>
       </c>
       <c r="C607" t="s">
         <v>8</v>
@@ -17335,10 +17477,10 @@
     </row>
     <row r="608" spans="1:6">
       <c r="A608" s="1" t="s">
-        <v>1219</v>
+        <v>1212</v>
       </c>
       <c r="B608" t="s">
-        <v>1220</v>
+        <v>1213</v>
       </c>
       <c r="C608" t="s">
         <v>8</v>
@@ -17355,10 +17497,10 @@
     </row>
     <row r="609" spans="1:6">
       <c r="A609" s="1" t="s">
-        <v>1221</v>
+        <v>1214</v>
       </c>
       <c r="B609" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="C609" t="s">
         <v>8</v>
@@ -17375,10 +17517,10 @@
     </row>
     <row r="610" spans="1:6">
       <c r="A610" s="1" t="s">
-        <v>1223</v>
+        <v>1216</v>
       </c>
       <c r="B610" t="s">
-        <v>1224</v>
+        <v>1217</v>
       </c>
       <c r="C610" t="s">
         <v>8</v>
@@ -17395,10 +17537,10 @@
     </row>
     <row r="611" spans="1:6">
       <c r="A611" s="1" t="s">
-        <v>1225</v>
+        <v>1218</v>
       </c>
       <c r="B611" t="s">
-        <v>1226</v>
+        <v>1219</v>
       </c>
       <c r="C611" t="s">
         <v>8</v>
@@ -17415,10 +17557,10 @@
     </row>
     <row r="612" spans="1:6">
       <c r="A612" s="1" t="s">
-        <v>1227</v>
+        <v>1220</v>
       </c>
       <c r="B612" t="s">
-        <v>1228</v>
+        <v>1221</v>
       </c>
       <c r="C612" t="s">
         <v>8</v>
@@ -17435,10 +17577,10 @@
     </row>
     <row r="613" spans="1:6">
       <c r="A613" s="1" t="s">
-        <v>1229</v>
+        <v>1222</v>
       </c>
       <c r="B613" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
       <c r="C613" t="s">
         <v>8</v>
@@ -17455,10 +17597,10 @@
     </row>
     <row r="614" spans="1:6">
       <c r="A614" s="1" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="B614" t="s">
-        <v>1232</v>
+        <v>1225</v>
       </c>
       <c r="C614" t="s">
         <v>8</v>
@@ -17475,10 +17617,10 @@
     </row>
     <row r="615" spans="1:6">
       <c r="A615" s="1" t="s">
-        <v>1233</v>
+        <v>1226</v>
       </c>
       <c r="B615" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
       <c r="C615" t="s">
         <v>8</v>
@@ -17495,10 +17637,10 @@
     </row>
     <row r="616" spans="1:6">
       <c r="A616" s="1" t="s">
-        <v>1235</v>
+        <v>1228</v>
       </c>
       <c r="B616" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
       <c r="C616" t="s">
         <v>8</v>
@@ -17515,10 +17657,10 @@
     </row>
     <row r="617" spans="1:6">
       <c r="A617" s="1" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="B617" t="s">
-        <v>1238</v>
+        <v>1231</v>
       </c>
       <c r="C617" t="s">
         <v>8</v>
@@ -17535,10 +17677,10 @@
     </row>
     <row r="618" spans="1:6">
       <c r="A618" s="1" t="s">
-        <v>1239</v>
+        <v>1232</v>
       </c>
       <c r="B618" t="s">
-        <v>1240</v>
+        <v>1233</v>
       </c>
       <c r="C618" t="s">
         <v>8</v>
@@ -17555,10 +17697,10 @@
     </row>
     <row r="619" spans="1:6">
       <c r="A619" s="1" t="s">
-        <v>1241</v>
+        <v>1234</v>
       </c>
       <c r="B619" t="s">
-        <v>1242</v>
+        <v>1235</v>
       </c>
       <c r="C619" t="s">
         <v>8</v>
@@ -17575,10 +17717,10 @@
     </row>
     <row r="620" spans="1:6">
       <c r="A620" s="1" t="s">
-        <v>1243</v>
+        <v>1236</v>
       </c>
       <c r="B620" t="s">
-        <v>1244</v>
+        <v>1237</v>
       </c>
       <c r="C620" t="s">
         <v>8</v>
@@ -17595,10 +17737,10 @@
     </row>
     <row r="621" spans="1:6">
       <c r="A621" s="1" t="s">
-        <v>1245</v>
+        <v>1238</v>
       </c>
       <c r="B621" t="s">
-        <v>1246</v>
+        <v>1239</v>
       </c>
       <c r="C621" t="s">
         <v>8</v>
@@ -17615,10 +17757,10 @@
     </row>
     <row r="622" spans="1:6">
       <c r="A622" s="1" t="s">
-        <v>1247</v>
+        <v>1240</v>
       </c>
       <c r="B622" t="s">
-        <v>1248</v>
+        <v>1241</v>
       </c>
       <c r="C622" t="s">
         <v>8</v>
@@ -17635,10 +17777,10 @@
     </row>
     <row r="623" spans="1:6">
       <c r="A623" s="1" t="s">
-        <v>1249</v>
+        <v>1242</v>
       </c>
       <c r="B623" t="s">
-        <v>1250</v>
+        <v>1243</v>
       </c>
       <c r="C623" t="s">
         <v>8</v>
@@ -17655,10 +17797,10 @@
     </row>
     <row r="624" spans="1:6">
       <c r="A624" s="1" t="s">
-        <v>1251</v>
+        <v>1244</v>
       </c>
       <c r="B624" t="s">
-        <v>1252</v>
+        <v>1245</v>
       </c>
       <c r="C624" t="s">
         <v>8</v>
@@ -17675,10 +17817,10 @@
     </row>
     <row r="625" spans="1:6">
       <c r="A625" s="1" t="s">
-        <v>1253</v>
+        <v>1246</v>
       </c>
       <c r="B625" t="s">
-        <v>1254</v>
+        <v>1247</v>
       </c>
       <c r="C625" t="s">
         <v>8</v>
@@ -17695,10 +17837,10 @@
     </row>
     <row r="626" spans="1:6">
       <c r="A626" s="1" t="s">
-        <v>1255</v>
+        <v>1248</v>
       </c>
       <c r="B626" t="s">
-        <v>1256</v>
+        <v>1249</v>
       </c>
       <c r="C626" t="s">
         <v>8</v>
@@ -17715,10 +17857,10 @@
     </row>
     <row r="627" spans="1:6">
       <c r="A627" s="1" t="s">
-        <v>1257</v>
+        <v>1250</v>
       </c>
       <c r="B627" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
       <c r="C627" t="s">
         <v>8</v>
@@ -17735,10 +17877,10 @@
     </row>
     <row r="628" spans="1:6">
       <c r="A628" s="1" t="s">
-        <v>1259</v>
+        <v>1252</v>
       </c>
       <c r="B628" t="s">
-        <v>1260</v>
+        <v>1253</v>
       </c>
       <c r="C628" t="s">
         <v>8</v>
@@ -17755,10 +17897,10 @@
     </row>
     <row r="629" spans="1:6">
       <c r="A629" s="1" t="s">
-        <v>1261</v>
+        <v>1254</v>
       </c>
       <c r="B629" t="s">
-        <v>1262</v>
+        <v>1255</v>
       </c>
       <c r="C629" t="s">
         <v>8</v>
@@ -17775,10 +17917,10 @@
     </row>
     <row r="630" spans="1:6">
       <c r="A630" s="1" t="s">
-        <v>1263</v>
+        <v>1256</v>
       </c>
       <c r="B630" t="s">
-        <v>1264</v>
+        <v>1257</v>
       </c>
       <c r="C630" t="s">
         <v>8</v>
@@ -17795,10 +17937,10 @@
     </row>
     <row r="631" spans="1:6">
       <c r="A631" s="1" t="s">
-        <v>1265</v>
+        <v>1258</v>
       </c>
       <c r="B631" t="s">
-        <v>1266</v>
+        <v>1259</v>
       </c>
       <c r="C631" t="s">
         <v>8</v>
@@ -17815,10 +17957,10 @@
     </row>
     <row r="632" spans="1:6">
       <c r="A632" s="1" t="s">
-        <v>1267</v>
+        <v>1260</v>
       </c>
       <c r="B632" t="s">
-        <v>1268</v>
+        <v>1261</v>
       </c>
       <c r="C632" t="s">
         <v>8</v>
@@ -17835,10 +17977,10 @@
     </row>
     <row r="633" spans="1:6">
       <c r="A633" s="1" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="B633" t="s">
-        <v>1270</v>
+        <v>1263</v>
       </c>
       <c r="C633" t="s">
         <v>8</v>
@@ -17855,10 +17997,10 @@
     </row>
     <row r="634" spans="1:6">
       <c r="A634" s="1" t="s">
-        <v>1271</v>
+        <v>1264</v>
       </c>
       <c r="B634" t="s">
-        <v>1272</v>
+        <v>1265</v>
       </c>
       <c r="C634" t="s">
         <v>8</v>
@@ -17875,10 +18017,10 @@
     </row>
     <row r="635" spans="1:6">
       <c r="A635" s="1" t="s">
-        <v>1273</v>
+        <v>1266</v>
       </c>
       <c r="B635" t="s">
-        <v>1274</v>
+        <v>1267</v>
       </c>
       <c r="C635" t="s">
         <v>8</v>
@@ -17895,10 +18037,10 @@
     </row>
     <row r="636" spans="1:6">
       <c r="A636" s="1" t="s">
-        <v>1275</v>
+        <v>1268</v>
       </c>
       <c r="B636" t="s">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="C636" t="s">
         <v>8</v>
@@ -17915,10 +18057,10 @@
     </row>
     <row r="637" spans="1:6">
       <c r="A637" s="1" t="s">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="B637" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="C637" t="s">
         <v>8</v>
@@ -17935,10 +18077,10 @@
     </row>
     <row r="638" spans="1:6">
       <c r="A638" s="1" t="s">
-        <v>1279</v>
+        <v>1272</v>
       </c>
       <c r="B638" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
       <c r="C638" t="s">
         <v>8</v>
@@ -17955,10 +18097,10 @@
     </row>
     <row r="639" spans="1:6">
       <c r="A639" s="1" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="B639" t="s">
-        <v>1282</v>
+        <v>1275</v>
       </c>
       <c r="C639" t="s">
         <v>8</v>
@@ -17975,10 +18117,10 @@
     </row>
     <row r="640" spans="1:6">
       <c r="A640" s="1" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="B640" t="s">
-        <v>1284</v>
+        <v>1277</v>
       </c>
       <c r="C640" t="s">
         <v>8</v>
@@ -17995,10 +18137,10 @@
     </row>
     <row r="641" spans="1:6">
       <c r="A641" s="1" t="s">
-        <v>1285</v>
+        <v>1278</v>
       </c>
       <c r="B641" t="s">
-        <v>1286</v>
+        <v>1279</v>
       </c>
       <c r="C641" t="s">
         <v>8</v>
@@ -18015,10 +18157,10 @@
     </row>
     <row r="642" spans="1:6">
       <c r="A642" s="1" t="s">
-        <v>1287</v>
+        <v>1280</v>
       </c>
       <c r="B642" t="s">
-        <v>1288</v>
+        <v>1281</v>
       </c>
       <c r="C642" t="s">
         <v>8</v>
@@ -18035,10 +18177,10 @@
     </row>
     <row r="643" spans="1:6">
       <c r="A643" s="1" t="s">
-        <v>1289</v>
+        <v>1282</v>
       </c>
       <c r="B643" t="s">
-        <v>1290</v>
+        <v>1283</v>
       </c>
       <c r="C643" t="s">
         <v>8</v>
@@ -18055,10 +18197,10 @@
     </row>
     <row r="644" spans="1:6">
       <c r="A644" s="1" t="s">
-        <v>1291</v>
+        <v>1284</v>
       </c>
       <c r="B644" t="s">
-        <v>1292</v>
+        <v>1285</v>
       </c>
       <c r="C644" t="s">
         <v>8</v>
@@ -18075,10 +18217,10 @@
     </row>
     <row r="645" spans="1:6">
       <c r="A645" s="1" t="s">
-        <v>1293</v>
+        <v>1286</v>
       </c>
       <c r="B645" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="C645" t="s">
         <v>8</v>
@@ -18095,10 +18237,10 @@
     </row>
     <row r="646" spans="1:6">
       <c r="A646" s="1" t="s">
-        <v>1295</v>
+        <v>1288</v>
       </c>
       <c r="B646" t="s">
-        <v>1296</v>
+        <v>1289</v>
       </c>
       <c r="C646" t="s">
         <v>8</v>
@@ -18115,10 +18257,10 @@
     </row>
     <row r="647" spans="1:6">
       <c r="A647" s="1" t="s">
-        <v>1297</v>
+        <v>1290</v>
       </c>
       <c r="B647" t="s">
-        <v>1298</v>
+        <v>1291</v>
       </c>
       <c r="C647" t="s">
         <v>8</v>
@@ -18135,10 +18277,10 @@
     </row>
     <row r="648" spans="1:6">
       <c r="A648" s="1" t="s">
-        <v>1299</v>
+        <v>1292</v>
       </c>
       <c r="B648" t="s">
-        <v>1300</v>
+        <v>1293</v>
       </c>
       <c r="C648" t="s">
         <v>8</v>
@@ -18155,10 +18297,10 @@
     </row>
     <row r="649" spans="1:6">
       <c r="A649" s="1" t="s">
-        <v>1301</v>
+        <v>1294</v>
       </c>
       <c r="B649" t="s">
-        <v>1302</v>
+        <v>1295</v>
       </c>
       <c r="C649" t="s">
         <v>8</v>
@@ -18175,10 +18317,10 @@
     </row>
     <row r="650" spans="1:6">
       <c r="A650" s="1" t="s">
-        <v>1303</v>
+        <v>1296</v>
       </c>
       <c r="B650" t="s">
-        <v>1304</v>
+        <v>1297</v>
       </c>
       <c r="C650" t="s">
         <v>8</v>
@@ -18195,10 +18337,10 @@
     </row>
     <row r="651" spans="1:6">
       <c r="A651" s="1" t="s">
-        <v>1305</v>
+        <v>1298</v>
       </c>
       <c r="B651" t="s">
-        <v>1306</v>
+        <v>1299</v>
       </c>
       <c r="C651" t="s">
         <v>8</v>
@@ -18215,10 +18357,10 @@
     </row>
     <row r="652" spans="1:6">
       <c r="A652" s="1" t="s">
-        <v>1307</v>
+        <v>1300</v>
       </c>
       <c r="B652" t="s">
-        <v>1308</v>
+        <v>1301</v>
       </c>
       <c r="C652" t="s">
         <v>8</v>
@@ -18235,10 +18377,10 @@
     </row>
     <row r="653" spans="1:6">
       <c r="A653" s="1" t="s">
-        <v>1309</v>
+        <v>1302</v>
       </c>
       <c r="B653" t="s">
-        <v>1310</v>
+        <v>1303</v>
       </c>
       <c r="C653" t="s">
         <v>8</v>
@@ -18255,10 +18397,10 @@
     </row>
     <row r="654" spans="1:6">
       <c r="A654" s="1" t="s">
-        <v>1311</v>
+        <v>1304</v>
       </c>
       <c r="B654" t="s">
-        <v>1312</v>
+        <v>1305</v>
       </c>
       <c r="C654" t="s">
         <v>8</v>
@@ -18275,10 +18417,10 @@
     </row>
     <row r="655" spans="1:6">
       <c r="A655" s="1" t="s">
-        <v>1313</v>
+        <v>1306</v>
       </c>
       <c r="B655" t="s">
-        <v>1314</v>
+        <v>1307</v>
       </c>
       <c r="C655" t="s">
         <v>8</v>
@@ -18295,10 +18437,10 @@
     </row>
     <row r="656" spans="1:6">
       <c r="A656" s="1" t="s">
-        <v>1315</v>
+        <v>1308</v>
       </c>
       <c r="B656" t="s">
-        <v>1316</v>
+        <v>1309</v>
       </c>
       <c r="C656" t="s">
         <v>8</v>
@@ -18315,10 +18457,10 @@
     </row>
     <row r="657" spans="1:6">
       <c r="A657" s="1" t="s">
-        <v>1317</v>
+        <v>1310</v>
       </c>
       <c r="B657" t="s">
-        <v>1318</v>
+        <v>1311</v>
       </c>
       <c r="C657" t="s">
         <v>8</v>
@@ -18335,10 +18477,10 @@
     </row>
     <row r="658" spans="1:6">
       <c r="A658" s="1" t="s">
-        <v>1319</v>
+        <v>1312</v>
       </c>
       <c r="B658" t="s">
-        <v>1320</v>
+        <v>1313</v>
       </c>
       <c r="C658" t="s">
         <v>8</v>
@@ -18355,10 +18497,10 @@
     </row>
     <row r="659" spans="1:6">
       <c r="A659" s="1" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
       <c r="B659" t="s">
-        <v>1322</v>
+        <v>1315</v>
       </c>
       <c r="C659" t="s">
         <v>8</v>
@@ -18375,10 +18517,10 @@
     </row>
     <row r="660" spans="1:6">
       <c r="A660" s="1" t="s">
-        <v>1323</v>
+        <v>1316</v>
       </c>
       <c r="B660" t="s">
-        <v>1324</v>
+        <v>1317</v>
       </c>
       <c r="C660" t="s">
         <v>8</v>
@@ -18395,10 +18537,10 @@
     </row>
     <row r="661" spans="1:6">
       <c r="A661" s="1" t="s">
-        <v>1325</v>
+        <v>1318</v>
       </c>
       <c r="B661" t="s">
-        <v>1326</v>
+        <v>1319</v>
       </c>
       <c r="C661" t="s">
         <v>8</v>
@@ -18415,10 +18557,10 @@
     </row>
     <row r="662" spans="1:6">
       <c r="A662" s="1" t="s">
-        <v>1327</v>
+        <v>1320</v>
       </c>
       <c r="B662" t="s">
-        <v>1328</v>
+        <v>1321</v>
       </c>
       <c r="C662" t="s">
         <v>8</v>
@@ -18435,10 +18577,10 @@
     </row>
     <row r="663" spans="1:6">
       <c r="A663" s="1" t="s">
-        <v>1329</v>
+        <v>1322</v>
       </c>
       <c r="B663" t="s">
-        <v>1330</v>
+        <v>1323</v>
       </c>
       <c r="C663" t="s">
         <v>8</v>
@@ -18455,10 +18597,10 @@
     </row>
     <row r="664" spans="1:6">
       <c r="A664" s="1" t="s">
-        <v>1331</v>
+        <v>1324</v>
       </c>
       <c r="B664" t="s">
-        <v>1332</v>
+        <v>1325</v>
       </c>
       <c r="C664" t="s">
         <v>8</v>
@@ -18475,10 +18617,10 @@
     </row>
     <row r="665" spans="1:6">
       <c r="A665" s="1" t="s">
-        <v>1333</v>
+        <v>1326</v>
       </c>
       <c r="B665" t="s">
-        <v>1334</v>
+        <v>1327</v>
       </c>
       <c r="C665" t="s">
         <v>8</v>
@@ -18495,10 +18637,10 @@
     </row>
     <row r="666" spans="1:6">
       <c r="A666" s="1" t="s">
-        <v>1335</v>
+        <v>1328</v>
       </c>
       <c r="B666" t="s">
-        <v>1336</v>
+        <v>1329</v>
       </c>
       <c r="C666" t="s">
         <v>8</v>
@@ -18515,10 +18657,10 @@
     </row>
     <row r="667" spans="1:6">
       <c r="A667" s="1" t="s">
-        <v>1337</v>
+        <v>1330</v>
       </c>
       <c r="B667" t="s">
-        <v>1338</v>
+        <v>1331</v>
       </c>
       <c r="C667" t="s">
         <v>8</v>
@@ -18535,10 +18677,10 @@
     </row>
     <row r="668" spans="1:6">
       <c r="A668" s="1" t="s">
-        <v>1339</v>
+        <v>1332</v>
       </c>
       <c r="B668" t="s">
-        <v>1340</v>
+        <v>1333</v>
       </c>
       <c r="C668" t="s">
         <v>8</v>
@@ -18555,10 +18697,10 @@
     </row>
     <row r="669" spans="1:6">
       <c r="A669" s="1" t="s">
-        <v>1341</v>
+        <v>1334</v>
       </c>
       <c r="B669" t="s">
-        <v>1342</v>
+        <v>1335</v>
       </c>
       <c r="C669" t="s">
         <v>8</v>
@@ -18575,10 +18717,10 @@
     </row>
     <row r="670" spans="1:6">
       <c r="A670" s="1" t="s">
-        <v>1343</v>
+        <v>1336</v>
       </c>
       <c r="B670" t="s">
-        <v>1344</v>
+        <v>1337</v>
       </c>
       <c r="C670" t="s">
         <v>8</v>
@@ -18595,10 +18737,10 @@
     </row>
     <row r="671" spans="1:6">
       <c r="A671" s="1" t="s">
-        <v>1345</v>
+        <v>1338</v>
       </c>
       <c r="B671" t="s">
-        <v>1346</v>
+        <v>1339</v>
       </c>
       <c r="C671" t="s">
         <v>8</v>
@@ -18615,10 +18757,10 @@
     </row>
     <row r="672" spans="1:6">
       <c r="A672" s="1" t="s">
-        <v>1347</v>
+        <v>1340</v>
       </c>
       <c r="B672" t="s">
-        <v>1348</v>
+        <v>1341</v>
       </c>
       <c r="C672" t="s">
         <v>8</v>
@@ -18635,19 +18777,19 @@
     </row>
     <row r="673" spans="1:6">
       <c r="A673" s="1" t="s">
-        <v>1349</v>
+        <v>1342</v>
       </c>
       <c r="B673" t="s">
-        <v>1350</v>
+        <v>1343</v>
       </c>
       <c r="C673" t="s">
         <v>8</v>
       </c>
       <c r="D673" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E673">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F673" t="s">
         <v>10</v>
@@ -18655,19 +18797,19 @@
     </row>
     <row r="674" spans="1:6">
       <c r="A674" s="1" t="s">
-        <v>1352</v>
+        <v>1344</v>
       </c>
       <c r="B674" t="s">
-        <v>1353</v>
+        <v>1345</v>
       </c>
       <c r="C674" t="s">
         <v>8</v>
       </c>
       <c r="D674" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E674">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F674" t="s">
         <v>10</v>
@@ -18675,19 +18817,19 @@
     </row>
     <row r="675" spans="1:6">
       <c r="A675" s="1" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
       <c r="B675" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
       <c r="C675" t="s">
         <v>8</v>
       </c>
       <c r="D675" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E675">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F675" t="s">
         <v>10</v>
@@ -18695,19 +18837,19 @@
     </row>
     <row r="676" spans="1:6">
       <c r="A676" s="1" t="s">
-        <v>1356</v>
+        <v>1348</v>
       </c>
       <c r="B676" t="s">
-        <v>1357</v>
+        <v>1349</v>
       </c>
       <c r="C676" t="s">
         <v>8</v>
       </c>
       <c r="D676" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E676">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F676" t="s">
         <v>10</v>
@@ -18715,19 +18857,19 @@
     </row>
     <row r="677" spans="1:6">
       <c r="A677" s="1" t="s">
-        <v>1358</v>
+        <v>1350</v>
       </c>
       <c r="B677" t="s">
-        <v>1359</v>
+        <v>1351</v>
       </c>
       <c r="C677" t="s">
         <v>8</v>
       </c>
       <c r="D677" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E677">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F677" t="s">
         <v>10</v>
@@ -18735,19 +18877,19 @@
     </row>
     <row r="678" spans="1:6">
       <c r="A678" s="1" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
       <c r="B678" t="s">
-        <v>1361</v>
+        <v>1353</v>
       </c>
       <c r="C678" t="s">
         <v>8</v>
       </c>
       <c r="D678" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E678">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F678" t="s">
         <v>10</v>
@@ -18755,19 +18897,19 @@
     </row>
     <row r="679" spans="1:6">
       <c r="A679" s="1" t="s">
-        <v>1362</v>
+        <v>1354</v>
       </c>
       <c r="B679" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
       <c r="C679" t="s">
         <v>8</v>
       </c>
       <c r="D679" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E679">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F679" t="s">
         <v>10</v>
@@ -18775,19 +18917,19 @@
     </row>
     <row r="680" spans="1:6">
       <c r="A680" s="1" t="s">
-        <v>1364</v>
+        <v>1356</v>
       </c>
       <c r="B680" t="s">
-        <v>1365</v>
+        <v>1357</v>
       </c>
       <c r="C680" t="s">
         <v>8</v>
       </c>
       <c r="D680" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E680">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F680" t="s">
         <v>10</v>
@@ -18795,19 +18937,19 @@
     </row>
     <row r="681" spans="1:6">
       <c r="A681" s="1" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
       <c r="B681" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
       <c r="C681" t="s">
         <v>8</v>
       </c>
       <c r="D681" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E681">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F681" t="s">
         <v>10</v>
@@ -18815,19 +18957,19 @@
     </row>
     <row r="682" spans="1:6">
       <c r="A682" s="1" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="B682" t="s">
-        <v>1369</v>
+        <v>1361</v>
       </c>
       <c r="C682" t="s">
         <v>8</v>
       </c>
       <c r="D682" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E682">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F682" t="s">
         <v>10</v>
@@ -18835,19 +18977,19 @@
     </row>
     <row r="683" spans="1:6">
       <c r="A683" s="1" t="s">
-        <v>1370</v>
+        <v>1362</v>
       </c>
       <c r="B683" t="s">
-        <v>693</v>
+        <v>1363</v>
       </c>
       <c r="C683" t="s">
         <v>8</v>
       </c>
       <c r="D683" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E683">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F683" t="s">
         <v>10</v>
@@ -18855,19 +18997,19 @@
     </row>
     <row r="684" spans="1:6">
       <c r="A684" s="1" t="s">
-        <v>1371</v>
+        <v>1364</v>
       </c>
       <c r="B684" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
       <c r="C684" t="s">
         <v>8</v>
       </c>
       <c r="D684" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E684">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F684" t="s">
         <v>10</v>
@@ -18875,19 +19017,19 @@
     </row>
     <row r="685" spans="1:6">
       <c r="A685" s="1" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="B685" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="C685" t="s">
         <v>8</v>
       </c>
       <c r="D685" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E685">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F685" t="s">
         <v>10</v>
@@ -18895,19 +19037,19 @@
     </row>
     <row r="686" spans="1:6">
       <c r="A686" s="1" t="s">
-        <v>1375</v>
+        <v>1368</v>
       </c>
       <c r="B686" t="s">
-        <v>1376</v>
+        <v>1369</v>
       </c>
       <c r="C686" t="s">
         <v>8</v>
       </c>
       <c r="D686" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E686">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F686" t="s">
         <v>10</v>
@@ -18915,19 +19057,19 @@
     </row>
     <row r="687" spans="1:6">
       <c r="A687" s="1" t="s">
-        <v>1377</v>
+        <v>1370</v>
       </c>
       <c r="B687" t="s">
-        <v>847</v>
+        <v>1371</v>
       </c>
       <c r="C687" t="s">
         <v>8</v>
       </c>
       <c r="D687" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E687">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F687" t="s">
         <v>10</v>
@@ -18935,19 +19077,19 @@
     </row>
     <row r="688" spans="1:6">
       <c r="A688" s="1" t="s">
-        <v>1378</v>
+        <v>1372</v>
       </c>
       <c r="B688" t="s">
-        <v>1379</v>
+        <v>1373</v>
       </c>
       <c r="C688" t="s">
         <v>8</v>
       </c>
       <c r="D688" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E688">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F688" t="s">
         <v>10</v>
@@ -18955,19 +19097,19 @@
     </row>
     <row r="689" spans="1:6">
       <c r="A689" s="1" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="B689" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="C689" t="s">
         <v>8</v>
       </c>
       <c r="D689" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E689">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F689" t="s">
         <v>10</v>
@@ -18975,19 +19117,19 @@
     </row>
     <row r="690" spans="1:6">
       <c r="A690" s="1" t="s">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="B690" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
       <c r="C690" t="s">
         <v>8</v>
       </c>
       <c r="D690" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E690">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F690" t="s">
         <v>10</v>
@@ -18995,19 +19137,19 @@
     </row>
     <row r="691" spans="1:6">
       <c r="A691" s="1" t="s">
-        <v>1384</v>
+        <v>1378</v>
       </c>
       <c r="B691" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
       <c r="C691" t="s">
         <v>8</v>
       </c>
       <c r="D691" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E691">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F691" t="s">
         <v>10</v>
@@ -19015,19 +19157,19 @@
     </row>
     <row r="692" spans="1:6">
       <c r="A692" s="1" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="B692" t="s">
-        <v>1387</v>
+        <v>1381</v>
       </c>
       <c r="C692" t="s">
         <v>8</v>
       </c>
       <c r="D692" t="s">
-        <v>1351</v>
+        <v>9</v>
       </c>
       <c r="E692">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F692" t="s">
         <v>10</v>
@@ -19035,21 +19177,541 @@
     </row>
     <row r="693" spans="1:6">
       <c r="A693" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B693" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C693" t="s">
+        <v>8</v>
+      </c>
+      <c r="D693" t="s">
+        <v>9</v>
+      </c>
+      <c r="E693">
+        <v>62</v>
+      </c>
+      <c r="F693" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6">
+      <c r="A694" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B694" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C694" t="s">
+        <v>8</v>
+      </c>
+      <c r="D694" t="s">
+        <v>9</v>
+      </c>
+      <c r="E694">
+        <v>62</v>
+      </c>
+      <c r="F694" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6">
+      <c r="A695" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C695" t="s">
+        <v>8</v>
+      </c>
+      <c r="D695" t="s">
+        <v>9</v>
+      </c>
+      <c r="E695">
+        <v>62</v>
+      </c>
+      <c r="F695" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6">
+      <c r="A696" s="1" t="s">
         <v>1388</v>
       </c>
-      <c r="B693" t="s">
+      <c r="B696" t="s">
         <v>1389</v>
       </c>
-      <c r="C693" t="s">
-        <v>8</v>
-      </c>
-      <c r="D693" t="s">
-        <v>1351</v>
-      </c>
-      <c r="E693">
+      <c r="C696" t="s">
+        <v>8</v>
+      </c>
+      <c r="D696" t="s">
+        <v>9</v>
+      </c>
+      <c r="E696">
+        <v>62</v>
+      </c>
+      <c r="F696" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6">
+      <c r="A697" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C697" t="s">
+        <v>8</v>
+      </c>
+      <c r="D697" t="s">
+        <v>9</v>
+      </c>
+      <c r="E697">
+        <v>62</v>
+      </c>
+      <c r="F697" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6">
+      <c r="A698" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C698" t="s">
+        <v>8</v>
+      </c>
+      <c r="D698" t="s">
+        <v>9</v>
+      </c>
+      <c r="E698">
+        <v>62</v>
+      </c>
+      <c r="F698" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6">
+      <c r="A699" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B699" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C699" t="s">
+        <v>8</v>
+      </c>
+      <c r="D699" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E699">
         <v>102</v>
       </c>
-      <c r="F693" t="s">
+      <c r="F699" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6">
+      <c r="A700" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B700" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C700" t="s">
+        <v>8</v>
+      </c>
+      <c r="D700" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E700">
+        <v>102</v>
+      </c>
+      <c r="F700" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6">
+      <c r="A701" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B701" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C701" t="s">
+        <v>8</v>
+      </c>
+      <c r="D701" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E701">
+        <v>102</v>
+      </c>
+      <c r="F701" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6">
+      <c r="A702" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B702" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C702" t="s">
+        <v>8</v>
+      </c>
+      <c r="D702" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E702">
+        <v>102</v>
+      </c>
+      <c r="F702" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6">
+      <c r="A703" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B703" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C703" t="s">
+        <v>8</v>
+      </c>
+      <c r="D703" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E703">
+        <v>102</v>
+      </c>
+      <c r="F703" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6">
+      <c r="A704" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B704" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C704" t="s">
+        <v>8</v>
+      </c>
+      <c r="D704" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E704">
+        <v>102</v>
+      </c>
+      <c r="F704" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6">
+      <c r="A705" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B705" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C705" t="s">
+        <v>8</v>
+      </c>
+      <c r="D705" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E705">
+        <v>102</v>
+      </c>
+      <c r="F705" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6">
+      <c r="A706" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B706" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C706" t="s">
+        <v>8</v>
+      </c>
+      <c r="D706" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E706">
+        <v>102</v>
+      </c>
+      <c r="F706" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6">
+      <c r="A707" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B707" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C707" t="s">
+        <v>8</v>
+      </c>
+      <c r="D707" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E707">
+        <v>102</v>
+      </c>
+      <c r="F707" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="708" spans="1:6">
+      <c r="A708" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B708" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C708" t="s">
+        <v>8</v>
+      </c>
+      <c r="D708" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E708">
+        <v>102</v>
+      </c>
+      <c r="F708" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="709" spans="1:6">
+      <c r="A709" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B709" t="s">
+        <v>697</v>
+      </c>
+      <c r="C709" t="s">
+        <v>8</v>
+      </c>
+      <c r="D709" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E709">
+        <v>102</v>
+      </c>
+      <c r="F709" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6">
+      <c r="A710" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B710" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C710" t="s">
+        <v>8</v>
+      </c>
+      <c r="D710" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E710">
+        <v>102</v>
+      </c>
+      <c r="F710" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6">
+      <c r="A711" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B711" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C711" t="s">
+        <v>8</v>
+      </c>
+      <c r="D711" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E711">
+        <v>102</v>
+      </c>
+      <c r="F711" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6">
+      <c r="A712" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B712" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C712" t="s">
+        <v>8</v>
+      </c>
+      <c r="D712" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E712">
+        <v>102</v>
+      </c>
+      <c r="F712" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="713" spans="1:6">
+      <c r="A713" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B713" t="s">
+        <v>853</v>
+      </c>
+      <c r="C713" t="s">
+        <v>8</v>
+      </c>
+      <c r="D713" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E713">
+        <v>102</v>
+      </c>
+      <c r="F713" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6">
+      <c r="A714" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B714" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C714" t="s">
+        <v>8</v>
+      </c>
+      <c r="D714" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E714">
+        <v>102</v>
+      </c>
+      <c r="F714" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="715" spans="1:6">
+      <c r="A715" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B715" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C715" t="s">
+        <v>8</v>
+      </c>
+      <c r="D715" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E715">
+        <v>102</v>
+      </c>
+      <c r="F715" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="716" spans="1:6">
+      <c r="A716" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B716" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C716" t="s">
+        <v>8</v>
+      </c>
+      <c r="D716" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E716">
+        <v>102</v>
+      </c>
+      <c r="F716" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="717" spans="1:6">
+      <c r="A717" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B717" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C717" t="s">
+        <v>8</v>
+      </c>
+      <c r="D717" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E717">
+        <v>102</v>
+      </c>
+      <c r="F717" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="718" spans="1:6">
+      <c r="A718" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B718" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C718" t="s">
+        <v>8</v>
+      </c>
+      <c r="D718" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E718">
+        <v>102</v>
+      </c>
+      <c r="F718" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6">
+      <c r="A719" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B719" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C719" t="s">
+        <v>8</v>
+      </c>
+      <c r="D719" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E719">
+        <v>102</v>
+      </c>
+      <c r="F719" t="s">
         <v>10</v>
       </c>
     </row>
